--- a/Lab/Card+Penalties.xlsx
+++ b/Lab/Card+Penalties.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="18350" windowHeight="6800"/>
   </bookViews>
